--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00782B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00782B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE4CE957-6655-435B-B293-57AB3E636924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DD36450-E1F3-445B-9732-14227EFAA79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4C7B45BA-9ABE-4347-8B11-677B057CEB4D}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{CC1FF775-14C8-4080-9E18-14CFFC4C8D47}"/>
   </bookViews>
   <sheets>
     <sheet name="00782B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1606,20 +1606,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A64FDF-4D5B-4158-AB7F-AB5E9AD0969A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1F20BF-1CB3-44F1-8B34-6ADF08B8A340}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1647,7 +1647,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1677,7 +1677,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1773,7 +1773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1853,7 +1853,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="51" t="s">
         <v>73</v>
       </c>
